--- a/outputs/51262.xlsx
+++ b/outputs/51262.xlsx
@@ -133,32 +133,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -414,140 +418,140 @@
   <dimension ref="B5:N14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="6" style="0" width="12.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="6" style="1" width="12.57"/>
   </cols>
   <sheetData>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F5" s="1" t="n">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F5" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="2" t="n">
         <v>44440</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="n">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="3" t="n">
         <v>44420</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <f aca="false">SUMPRODUCT(SUMIFS($D$6:$D$13,$B$6:$B$13,"&gt;="&amp;DATE(YEAR(F5),MONTH(F5),1),$B$6:$B$13,"&lt;="&amp;DATE(YEAR(F5),MONTH(F5),31),$C$6:$C$13,$F$10:$F$14))</f>
+      <c r="D6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <f aca="false">SUMPRODUCT(($B$6:$B$13&gt;=DATE(YEAR(F5),MONTH(F5),1))*($B$6:$B$13&lt;=DATE(YEAR(F5),MONTH(F5),31))*ISNUMBER(MATCH($C$6:$C$13,$F$10:$F$14,0))*$D$6:$D$13)</f>
         <v>30</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <f aca="false">SUMPRODUCT(SUMIFS($D$6:$D$13,$B$6:$B$13,"&gt;="&amp;DATE(YEAR(G5),MONTH(G5),1),$B$6:$B$13,"&lt;="&amp;DATE(YEAR(G5),MONTH(G5),31),$C$6:$C$13,$F$10:$F$14))</f>
+      <c r="G6" s="5" t="n">
+        <f aca="false">SUMPRODUCT(($B$6:$B$13&gt;=DATE(YEAR(G5),MONTH(G5),1))*($B$6:$B$13&lt;=DATE(YEAR(G5),MONTH(G5),31))*ISNUMBER(MATCH($C$6:$C$13,$F$10:$F$14,0))*$D$6:$D$13)</f>
         <v>20</v>
       </c>
-      <c r="H6" s="4" t="n">
-        <f aca="false">SUMPRODUCT(SUMIFS($D$6:$D$13,$B$6:$B$13,"&gt;="&amp;DATE(YEAR(H5),MONTH(H5),1),$B$6:$B$13,"&lt;="&amp;DATE(YEAR(H5),MONTH(H5),31),$C$6:$C$13,$F$10:$F$14))</f>
+      <c r="H6" s="5" t="n">
+        <f aca="false">SUMPRODUCT(($B$6:$B$13&gt;=DATE(YEAR(H5),MONTH(H5),1))*($B$6:$B$13&lt;=DATE(YEAR(H5),MONTH(H5),31))*ISNUMBER(MATCH($C$6:$C$13,$F$10:$F$14,0))*$D$6:$D$13)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="n">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="3" t="n">
         <v>44420</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="n">
+      <c r="D7" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="3" t="n">
         <v>44420</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="3" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="n">
+      <c r="D8" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="3" t="n">
         <v>44420</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="D9" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="n">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="3" t="n">
         <v>44420</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="s">
+      <c r="D10" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="n">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="3" t="n">
         <v>44459</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="s">
+      <c r="D11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2" t="n">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="3" t="n">
         <v>44469</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="n">
+      <c r="D12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="3" t="n">
         <v>44445</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="6"/>
+      <c r="D13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F14" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
